--- a/inputs/production_plan.xlsx
+++ b/inputs/production_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Product</t>
   </si>
@@ -23,6 +23,12 @@
   </si>
   <si>
     <t>Production Qty</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>2000</t>
   </si>
 </sst>
 </file>
@@ -380,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -395,36 +401,11 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
-        <v>189</v>
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
-      <c r="B2">
-        <v>2000</v>
-      </c>
-      <c r="C2">
-        <v>2364</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>189</v>
-      </c>
-      <c r="B3">
-        <v>3108</v>
-      </c>
-      <c r="C3">
-        <v>2474</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>222</v>
-      </c>
-      <c r="B4">
-        <v>345</v>
-      </c>
-      <c r="C4">
-        <v>2846</v>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/production_plan.xlsx
+++ b/inputs/production_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Product</t>
   </si>
@@ -23,12 +23,6 @@
   </si>
   <si>
     <t>Production Qty</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>2000</t>
   </si>
 </sst>
 </file>
@@ -386,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -400,14 +394,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
